--- a/survey_templates/044_future_planning_questionnaire--survey_templates.xlsx
+++ b/survey_templates/044_future_planning_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>future_planning_questionnaire</t>
+          <t>future_goal_questionnaire</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>future_planning_questionnaire</t>
+          <t>future goals</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>future_planning_questionnaire_section1</t>
+          <t>current_goals_question</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_are_your_future_goals</t>
+          <t>current goals</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>future_planning_questionnaire_section2</t>
+          <t>short_term_goal_description</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>goals_and_objectives</t>
+          <t>short-term goals description</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>date_of_goal</t>
+          <t>long_term_goal_description</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>date_of_goal</t>
+          <t>long-term goals description</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>description_of_goal</t>
+          <t>planning_style_question</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>description_of_goal</t>
+          <t>planning style</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>goal_1</t>
+          <t>current_planning_method_question</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>goal_1</t>
+          <t>current planning method</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>goal_2</t>
+          <t>current_skills_question</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>goal_2</t>
+          <t>current skills</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>goal_3</t>
+          <t>future_skills_question</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>goal_3</t>
+          <t>future skills</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>goal_4</t>
+          <t>time_management_question</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>goal_4</t>
+          <t>time management</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>goal_5</t>
+          <t>priorities_question</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>goal_5</t>
+          <t>priorities</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>goal_6</t>
+          <t>next_steps_question</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>goal_6</t>
+          <t>next steps</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>goal_7</t>
+          <t>reflection_question</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>goal_7</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>goal_8</t>
+          <t>values_question</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>goal_8</t>
+          <t>values</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>goal_9</t>
+          <t>hobby_activity_question</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>goal_9</t>
+          <t>hobby activity</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>goal_10</t>
+          <t>future_planning_questionnaire_section1_hint</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>goal_10</t>
+          <t>Future Planning Questionnaire Section1 Hint</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>future_planning_questionnaire_section1_hint</t>
+          <t>future_planning_questionnaire_section2_hint</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>what_are_your_current_goals</t>
+          <t>Future Planning Questionnaire Section2 Hint</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>future_planning_questionnaire_section2_hint</t>
+          <t>future_planning_questionnaire_section3_hint</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>what_are_your_values</t>
+          <t>Future Planning Questionnaire Section3 Hint</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>future_planning_questionnaire_section3_hint</t>
+          <t>future_planning_questionnaire_section4_hint</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>what_are_your_values</t>
+          <t>Future Planning Questionnaire Section4 Hint</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>future_planning_questionnaire_section4_hint</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>what_are_your_current_skills</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>future_planning_questionnaire_section5_hint</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>what_are_your_current_skills</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>future_planning_questionnaire_section6_hint</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>what_are_your_future_planning_style</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>future_planning_questionnaire_section7_hint</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>what_are_your_current_planning_method</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>future_planning_questionnaire_section8_hint</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>what_are_your_future_planning_method</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>future_planning_questionnaire_section9_hint</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>what_are_your_future_planning_method</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>future_planning_questionnaire_section10_hint</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>what_are_your_future_planning_method</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,476 +965,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>future_planning_questionnaire_choices</t>
+          <t>future_goal_questionnaire_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>future_planning_questionnaire_choices</t>
+          <t>future_goal_questionnaire_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>future_planning_questionnaire_choices</t>
+          <t>future_goal_questionnaire_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>future_planning_questionnaire_section2_choices</t>
+          <t>planning_style_question_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>future_planning_questionnaire_section2_choices</t>
+          <t>planning_style_question_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>future_planning_questionnaire_section2_choices</t>
+          <t>planning_style_question_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>goal_1_choices</t>
+          <t>time_management_question_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>goal_1_choices</t>
+          <t>time_management_question_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>goal_2_choices</t>
+          <t>time_management_question_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>goal_2_choices</t>
+          <t>hobby_activity_question_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>goal_3_choices</t>
+          <t>hobby_activity_question_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>goal_3_choices</t>
+          <t>hobby_activity_question_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>goal_4_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>goal_4_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>goal_5_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>goal_5_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>goal_6_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>goal_6_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>goal_7_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>goal_7_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>goal_8_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>goal_8_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>goal_9_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>goal_9_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>goal_10_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>goal_10_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>future_planning_questionnaire_section6_hint_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>future_planning_questionnaire_section6_hint_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
